--- a/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,95</t>
+          <t>0,0; 52,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 8,63</t>
+          <t>-5,27; 8,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 6,73</t>
+          <t>-5,31; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 10,78</t>
+          <t>0,13; 10,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 5,81</t>
+          <t>-3,2; 5,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,03; 260,02</t>
+          <t>-54,61; 235,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 276,62</t>
+          <t>-74,08; 221,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,3; —</t>
+          <t>-49,83; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 7,23</t>
+          <t>-4,03; 7,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,91</t>
+          <t>-1,47; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,24</t>
+          <t>-4,06; 2,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,21</t>
+          <t>-3,82; 3,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 207,54</t>
+          <t>-48,55; 190,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 388,03</t>
+          <t>-34,95; 355,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 140,58</t>
+          <t>-70,19; 120,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,14; 198,42</t>
+          <t>-75,86; 183,82</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,3</t>
+          <t>-2,52; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,74</t>
+          <t>-4,36; 1,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,57</t>
+          <t>-1,63; 4,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 0,18</t>
+          <t>-8,43; 0,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 187,39</t>
+          <t>-64,37; 238,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,61; 154,4</t>
+          <t>-88,5; 141,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 934,51</t>
+          <t>-72,21; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,97</t>
+          <t>-100,0; 68,57</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,63</t>
+          <t>-1,69; 3,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,87</t>
+          <t>-1,85; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,49</t>
+          <t>-0,93; 3,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,86</t>
+          <t>-4,22; 0,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 112,01</t>
+          <t>-29,28; 108,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 104,03</t>
+          <t>-40,03; 101,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 224,81</t>
+          <t>-26,32; 211,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 48,89</t>
+          <t>-76,9; 55,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,54</t>
+          <t>0,0; 58,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 8,3</t>
+          <t>-5,46; 8,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 6,38</t>
+          <t>-5,4; 6,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 10,4</t>
+          <t>0,1; 10,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,48</t>
+          <t>-3,14; 5,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 235,94</t>
+          <t>-53,5; 198,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,08; 221,66</t>
+          <t>-75,21; 296,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,83; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 7,48</t>
+          <t>-4,55; 7,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,91</t>
+          <t>-1,74; 7,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 2,82</t>
+          <t>-4,39; 3,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,46</t>
+          <t>-4,02; 3,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 190,3</t>
+          <t>-53,56; 197,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 355,09</t>
+          <t>-39,58; 388,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 120,85</t>
+          <t>-71,41; 160,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 183,82</t>
+          <t>-79,7; 167,19</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,21</t>
+          <t>-2,89; 2,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,39</t>
+          <t>-4,01; 1,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,77</t>
+          <t>-1,7; 4,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 0,21</t>
+          <t>-9,42; 0,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,37; 238,81</t>
+          <t>-67,07; 176,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,5; 141,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,21; —</t>
+          <t>-71,08; 799,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,57</t>
+          <t>-100,0; 51,26</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,8</t>
+          <t>-1,93; 3,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,7</t>
+          <t>-1,98; 2,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,36</t>
+          <t>-1,13; 3,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,92</t>
+          <t>-4,34; 0,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 108,92</t>
+          <t>-32,14; 98,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 101,22</t>
+          <t>-39,02; 110,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 211,14</t>
+          <t>-31,49; 190,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 55,14</t>
+          <t>-74,56; 49,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,72</t>
+          <t>13,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,61</t>
+          <t>0,0; 51,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 8,1</t>
+          <t>-5,51; 8,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 6,76</t>
+          <t>-5,08; 6,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 10,19</t>
+          <t>0,15; 10,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,8</t>
+          <t>-2,47; 6,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 198,54</t>
+          <t>-54,03; 260,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,21; 296,04</t>
+          <t>-70,41; 276,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,3; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-14,8%</t>
+          <t>-15,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 7,85</t>
+          <t>-4,41; 7,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,47</t>
+          <t>-1,6; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 3,27</t>
+          <t>-4,1; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,15</t>
+          <t>-3,96; 3,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 197,43</t>
+          <t>-47,01; 207,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 388,47</t>
+          <t>-38,52; 388,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,41; 160,81</t>
+          <t>-69,17; 140,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,7; 167,19</t>
+          <t>-78,99; 218,94</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-72,85%</t>
+          <t>-73,32%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,92</t>
+          <t>-2,56; 3,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,74</t>
+          <t>-4,35; 1,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,54</t>
+          <t>-1,55; 4,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 0,21</t>
+          <t>-8,99; 0,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,07; 176,66</t>
+          <t>-67,29; 187,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,61; 154,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 799,78</t>
+          <t>-68,22; 934,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,26</t>
+          <t>-100,0; 43,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-34,5%</t>
+          <t>-35,39%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,47</t>
+          <t>-1,57; 3,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,68</t>
+          <t>-2,2; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,23</t>
+          <t>-0,98; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,9</t>
+          <t>-4,98; 0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 98,14</t>
+          <t>-27,65; 112,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 110,87</t>
+          <t>-43,37; 104,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 190,32</t>
+          <t>-29,56; 224,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 49,21</t>
+          <t>-80,66; 46,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>13.3006385973225</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +644,136 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 51,62</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>51.61985925006211</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,19</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>275,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,51; 8,63</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,08; 6,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,15; 10,78</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 6,05</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-54,03; 260,02</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-70,41; 276,62</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-66,3; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.478277603554548</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4558956323029426</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>4.191462240732345</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.113948198955725</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2140948015012944</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.08741790882280102</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2.758721017173758</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.5091068322165248</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-11,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-15,05%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.514358019947455</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.079197633152678</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1460841613715286</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.472507445869872</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5403321025393959</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7041306040590035</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6629546411234369</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 7,23</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,6; 6,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,1; 3,24</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 3,32</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-47,01; 207,54</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-38,52; 388,03</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-69,17; 140,58</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-78,99; 218,94</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.627067610144097</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.727121111103972</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10.77863937052298</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.051490189950997</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.600193639386668</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.766226908238555</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +781,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-35,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-73,32%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.288453236315881</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.479856665525622</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4649526398151242</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5447726618480746</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1970206437493316</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.6655707916888046</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1131351481711796</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1504822823085016</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 3,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,35; 1,74</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,55; 4,57</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,99; 0,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-67,29; 187,39</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-88,61; 154,4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-68,22; 934,51</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 43,87</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.406661213616086</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.603544422876349</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.096491210686523</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.963630042521007</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4700784614282625</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3851631480764049</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6916578113021975</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7898790207929256</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.23208290198264</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.91281528459127</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.242941111845769</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.317396461749378</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.07538405588893</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.88030157765694</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.405759966637142</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.189413053420389</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2982920736319724</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.025826399626583</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.382569642009188</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.646448398990382</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1034863491035484</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3560569717857451</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.7984566084565049</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.7331884324115884</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.560900839248806</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.346061763897265</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.55232557816969</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.986115571318527</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6728634195050468</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8861229933088792</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6822207599331848</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.302515836698289</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.742185285998298</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.566866200082876</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.0860228404762902</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.873884129374446</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.543996599762534</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>9.34505787192375</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4387231596604353</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-35,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 3,63</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 2,87</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,98; 3,49</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; 0,83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-27,65; 112,01</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-43,37; 104,03</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-29,56; 224,81</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-80,66; 46,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.8787124413446652</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4448692499210684</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.169473112872999</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.192126196924952</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1819113149722423</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1180711723481298</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.4420876906362824</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.3539366863001872</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.574532706912602</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.204999073967761</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.97955425636728</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.983185191467434</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2764832455049856</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4337334115989743</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2956085855526211</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.8066301299534092</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.627750789319445</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.871438786975572</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.489782038389122</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.8330199795247242</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.120076726868758</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.040336738483317</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.248101233475155</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.465908947781777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1079,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
